--- a/release_forms/046_mental_health_care_release_of_information_form--release_forms.xlsx
+++ b/release_forms/046_mental_health_care_release_of_information_form--release_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'kaiser'}</t>
+          <t>kaiser</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Kaiser'}</t>
+          <t>Kaiser</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'hospital'}</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Hospital'}</t>
+          <t>Hospital</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'clinic'}</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Clinic'}</t>
+          <t>Clinic</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'cardiology'}</t>
+          <t>cardiology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Cardiology'}</t>
+          <t>Cardiology</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'dermatology'}</t>
+          <t>dermatology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Dermatology'}</t>
+          <t>Dermatology</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'gastroenterology'}</t>
+          <t>gastroenterology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Gastroenterology'}</t>
+          <t>Gastroenterology</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'cardiologist'}</t>
+          <t>cardiologist</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Cardiologist'}</t>
+          <t>Cardiologist</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'dermatologist'}</t>
+          <t>dermatologist</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Dermatologist'}</t>
+          <t>Dermatologist</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'gastroenterologist'}</t>
+          <t>gastroenterologist</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Gastroenterologist'}</t>
+          <t>Gastroenterologist</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'electronic'}</t>
+          <t>electronic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Electronic'}</t>
+          <t>Electronic</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'paper'}</t>
+          <t>paper</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Paper'}</t>
+          <t>Paper</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'patient'}</t>
+          <t>patient</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Patient'}</t>
+          <t>Patient</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'family_member'}</t>
+          <t>family_member</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Family Member'}</t>
+          <t>Family Member</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'healthcare_provider'}</t>
+          <t>healthcare_provider</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Healthcare Provider'}</t>
+          <t>Healthcare Provider</t>
         </is>
       </c>
     </row>
